--- a/aec/results/신촌/linear_results.xlsx
+++ b/aec/results/신촌/linear_results.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단변량_univariate" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다변량_coefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다변량_model_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="단변량_univariate" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="다변량_coefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="다변량_model_summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/aec/results/신촌/linear_results.xlsx
+++ b/aec/results/신촌/linear_results.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="단변량_univariate" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="다변량_coefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="다변량_model_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단변량_univariate" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다변량_coefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="다변량_model_summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,28 +484,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.7066</v>
+        <v>43.5075</v>
       </c>
       <c r="C2" t="n">
-        <v>41.3257</v>
+        <v>41.081</v>
       </c>
       <c r="D2" t="n">
-        <v>46.0876</v>
+        <v>45.934</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2137</v>
+        <v>1.2369</v>
       </c>
       <c r="F2" t="n">
-        <v>36.0121</v>
+        <v>35.1761</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5004</v>
+        <v>0.4949</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5</v>
+        <v>0.4945</v>
       </c>
     </row>
     <row r="3">
@@ -515,28 +515,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-2.1201</v>
+        <v>-2.5411</v>
       </c>
       <c r="C3" t="n">
-        <v>-3.8004</v>
+        <v>-4.2424</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4399</v>
+        <v>-0.8399</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8565</v>
+        <v>0.8672</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.4754</v>
+        <v>-2.9304</v>
       </c>
       <c r="G3" t="n">
-        <v>0.013436</v>
+        <v>0.003447</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0047</v>
+        <v>0.0068</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0039</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="4">
@@ -546,28 +546,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.3803</v>
+        <v>7.7203</v>
       </c>
       <c r="C4" t="n">
-        <v>5.7449</v>
+        <v>6.0673</v>
       </c>
       <c r="D4" t="n">
-        <v>9.0158</v>
+        <v>9.373200000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8336</v>
+        <v>0.8426</v>
       </c>
       <c r="F4" t="n">
-        <v>8.8531</v>
+        <v>9.1629</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0571</v>
+        <v>0.0623</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0563</v>
+        <v>0.0616</v>
       </c>
     </row>
     <row r="5">
@@ -577,28 +577,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-3.7464</v>
+        <v>-3.8882</v>
       </c>
       <c r="C5" t="n">
-        <v>-5.4181</v>
+        <v>-5.5816</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.0746</v>
+        <v>-2.1947</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8522</v>
+        <v>0.8632</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.3963</v>
+        <v>-4.5043</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2e-05</v>
+        <v>7e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0147</v>
+        <v>0.0158</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0139</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="6">
@@ -608,28 +608,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.0374</v>
+        <v>-1.5748</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.7207</v>
+        <v>-3.2797</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6458</v>
+        <v>0.13</v>
       </c>
       <c r="E6" t="n">
-        <v>0.858</v>
+        <v>0.869</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2091</v>
+        <v>-1.8123</v>
       </c>
       <c r="G6" t="n">
-        <v>0.226853</v>
+        <v>0.07018000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0011</v>
+        <v>0.0026</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0004</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="7">
@@ -639,28 +639,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1148</v>
+        <v>3.1323</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4392</v>
+        <v>1.434</v>
       </c>
       <c r="D7" t="n">
-        <v>4.7905</v>
+        <v>4.8305</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8541</v>
+        <v>0.8656</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6468</v>
+        <v>3.6185</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000276</v>
+        <v>0.000308</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0102</v>
+        <v>0.0103</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0094</v>
+        <v>0.0095</v>
       </c>
     </row>
     <row r="8">
@@ -670,28 +670,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.0355</v>
+        <v>7.3935</v>
       </c>
       <c r="C8" t="n">
-        <v>5.3955</v>
+        <v>5.736</v>
       </c>
       <c r="D8" t="n">
-        <v>8.6754</v>
+        <v>9.051</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8359</v>
+        <v>0.8449</v>
       </c>
       <c r="F8" t="n">
-        <v>8.4162</v>
+        <v>8.750999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0519</v>
+        <v>0.0572</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0511</v>
+        <v>0.0564</v>
       </c>
     </row>
     <row r="9">
@@ -722,17 +722,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>F=1.573</t>
+          <t>F=1.68</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.009261</v>
+        <v>0.003585</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0547</v>
+        <v>0.0584</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0199</v>
+        <v>0.0237</v>
       </c>
     </row>
   </sheetData>
@@ -746,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,22 +793,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>93.8464</v>
+        <v>94.0565</v>
       </c>
       <c r="C2" t="n">
-        <v>53.7777</v>
+        <v>54.0572</v>
       </c>
       <c r="D2" t="n">
-        <v>133.9151</v>
+        <v>134.0559</v>
       </c>
       <c r="E2" t="n">
-        <v>20.4237</v>
+        <v>20.3878</v>
       </c>
       <c r="F2" t="n">
-        <v>4.595</v>
+        <v>4.6134</v>
       </c>
       <c r="G2" t="n">
-        <v>5e-06</v>
+        <v>4e-06</v>
       </c>
     </row>
     <row r="3">
@@ -818,19 +818,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.464</v>
+        <v>42.0604</v>
       </c>
       <c r="C3" t="n">
-        <v>40.1201</v>
+        <v>39.692</v>
       </c>
       <c r="D3" t="n">
-        <v>44.808</v>
+        <v>44.4287</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1948</v>
+        <v>1.2072</v>
       </c>
       <c r="F3" t="n">
-        <v>35.5422</v>
+        <v>34.8422</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -843,19 +843,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-4.4207</v>
+        <v>-4.6031</v>
       </c>
       <c r="C4" t="n">
-        <v>-5.6094</v>
+        <v>-5.7954</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.232</v>
+        <v>-3.4107</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6059</v>
+        <v>0.6077</v>
       </c>
       <c r="F4" t="n">
-        <v>-7.2959</v>
+        <v>-7.574</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -868,22 +868,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-8.3621</v>
+        <v>-12.6516</v>
       </c>
       <c r="C5" t="n">
-        <v>-17.3972</v>
+        <v>-22.2665</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6729000000000001</v>
+        <v>-3.0368</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6053</v>
+        <v>4.9007</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8158</v>
+        <v>-2.5816</v>
       </c>
       <c r="G5" t="n">
-        <v>0.069648</v>
+        <v>0.009951</v>
       </c>
     </row>
     <row r="6">
@@ -893,22 +893,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-2.8807</v>
+        <v>-3.6768</v>
       </c>
       <c r="C6" t="n">
-        <v>-4.7753</v>
+        <v>-5.6132</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9861</v>
+        <v>-1.7404</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9657</v>
+        <v>0.987</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.983</v>
+        <v>-3.7253</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00291</v>
+        <v>0.000204</v>
       </c>
     </row>
     <row r="7">
@@ -918,22 +918,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.4917</v>
+        <v>1.3528</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0835</v>
+        <v>-0.0585</v>
       </c>
       <c r="D7" t="n">
-        <v>2.8999</v>
+        <v>2.764</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7178</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0782</v>
+        <v>1.8807</v>
       </c>
       <c r="G7" t="n">
-        <v>0.037894</v>
+        <v>0.060258</v>
       </c>
     </row>
     <row r="8">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.4559</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.7165</v>
+        <v>-0.8545</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8466</v>
+        <v>1.7664</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6532</v>
+        <v>0.6679</v>
       </c>
       <c r="F8" t="n">
-        <v>0.865</v>
+        <v>0.6826</v>
       </c>
       <c r="G8" t="n">
-        <v>0.387222</v>
+        <v>0.494981</v>
       </c>
     </row>
     <row r="9">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14.6558</v>
+        <v>19.0328</v>
       </c>
       <c r="C9" t="n">
-        <v>5.9013</v>
+        <v>9.6714</v>
       </c>
       <c r="D9" t="n">
-        <v>23.4103</v>
+        <v>28.3942</v>
       </c>
       <c r="E9" t="n">
-        <v>4.4623</v>
+        <v>4.7715</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2844</v>
+        <v>3.9888</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001051</v>
+        <v>6.999999999999999e-05</v>
       </c>
     </row>
     <row r="10">
@@ -993,22 +993,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.6128</v>
+        <v>28.1679</v>
       </c>
       <c r="C10" t="n">
-        <v>-21.535</v>
+        <v>-20.889</v>
       </c>
       <c r="D10" t="n">
-        <v>76.7606</v>
+        <v>77.22490000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>25.0514</v>
+        <v>25.0045</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1022</v>
+        <v>1.1265</v>
       </c>
       <c r="G10" t="n">
-        <v>0.270569</v>
+        <v>0.260171</v>
       </c>
     </row>
     <row r="11">
@@ -1018,22 +1018,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11.5943</v>
+        <v>13.3509</v>
       </c>
       <c r="C11" t="n">
-        <v>-29.9361</v>
+        <v>-28.3212</v>
       </c>
       <c r="D11" t="n">
-        <v>53.1248</v>
+        <v>55.023</v>
       </c>
       <c r="E11" t="n">
-        <v>21.1688</v>
+        <v>21.2404</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5477</v>
+        <v>0.6286</v>
       </c>
       <c r="G11" t="n">
-        <v>0.583989</v>
+        <v>0.529755</v>
       </c>
     </row>
     <row r="12">
@@ -1043,22 +1043,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.9115</v>
+        <v>24.3304</v>
       </c>
       <c r="C12" t="n">
-        <v>-31.7991</v>
+        <v>-32.2852</v>
       </c>
       <c r="D12" t="n">
-        <v>81.622</v>
+        <v>80.946</v>
       </c>
       <c r="E12" t="n">
-        <v>28.9063</v>
+        <v>28.8572</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8618</v>
+        <v>0.8431</v>
       </c>
       <c r="G12" t="n">
-        <v>0.388964</v>
+        <v>0.399321</v>
       </c>
     </row>
     <row r="13">
@@ -1068,22 +1068,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26.0656</v>
+        <v>26.4072</v>
       </c>
       <c r="C13" t="n">
-        <v>-15.6502</v>
+        <v>-15.2313</v>
       </c>
       <c r="D13" t="n">
-        <v>67.7814</v>
+        <v>68.0457</v>
       </c>
       <c r="E13" t="n">
-        <v>21.2632</v>
+        <v>21.2233</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2259</v>
+        <v>1.2443</v>
       </c>
       <c r="G13" t="n">
-        <v>0.220486</v>
+        <v>0.213646</v>
       </c>
     </row>
     <row r="14">
@@ -1093,22 +1093,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13.9427</v>
+        <v>14.5463</v>
       </c>
       <c r="C14" t="n">
-        <v>-29.3639</v>
+        <v>-28.6789</v>
       </c>
       <c r="D14" t="n">
-        <v>57.2493</v>
+        <v>57.7714</v>
       </c>
       <c r="E14" t="n">
-        <v>22.0741</v>
+        <v>22.032</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6602</v>
       </c>
       <c r="G14" t="n">
-        <v>0.527743</v>
+        <v>0.50923</v>
       </c>
     </row>
     <row r="15">
@@ -1118,22 +1118,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33.8231</v>
+        <v>32.9587</v>
       </c>
       <c r="C15" t="n">
-        <v>-15.4045</v>
+        <v>-16.1999</v>
       </c>
       <c r="D15" t="n">
-        <v>83.05070000000001</v>
+        <v>82.1173</v>
       </c>
       <c r="E15" t="n">
-        <v>25.0921</v>
+        <v>25.0563</v>
       </c>
       <c r="F15" t="n">
-        <v>1.348</v>
+        <v>1.3154</v>
       </c>
       <c r="G15" t="n">
-        <v>0.177918</v>
+        <v>0.18863</v>
       </c>
     </row>
     <row r="16">
@@ -1143,22 +1143,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14.562</v>
+        <v>13.6122</v>
       </c>
       <c r="C16" t="n">
-        <v>-42.1283</v>
+        <v>-42.9758</v>
       </c>
       <c r="D16" t="n">
-        <v>71.25239999999999</v>
+        <v>70.2002</v>
       </c>
       <c r="E16" t="n">
-        <v>28.896</v>
+        <v>28.8431</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5039</v>
+        <v>0.4719</v>
       </c>
       <c r="G16" t="n">
-        <v>0.614389</v>
+        <v>0.637055</v>
       </c>
     </row>
     <row r="17">
@@ -1168,22 +1168,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9.0937</v>
+        <v>8.6311</v>
       </c>
       <c r="C17" t="n">
-        <v>-32.4501</v>
+        <v>-32.9467</v>
       </c>
       <c r="D17" t="n">
-        <v>50.6375</v>
+        <v>50.2089</v>
       </c>
       <c r="E17" t="n">
-        <v>21.1756</v>
+        <v>21.1924</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4294</v>
+        <v>0.4073</v>
       </c>
       <c r="G17" t="n">
-        <v>0.667677</v>
+        <v>0.683879</v>
       </c>
     </row>
     <row r="18">
@@ -1193,22 +1193,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31.5863</v>
+        <v>31.8979</v>
       </c>
       <c r="C18" t="n">
-        <v>-17.5743</v>
+        <v>-17.1764</v>
       </c>
       <c r="D18" t="n">
-        <v>80.7469</v>
+        <v>80.9722</v>
       </c>
       <c r="E18" t="n">
-        <v>25.058</v>
+        <v>25.0134</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2605</v>
+        <v>1.2752</v>
       </c>
       <c r="G18" t="n">
-        <v>0.207715</v>
+        <v>0.202471</v>
       </c>
     </row>
     <row r="19">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.5198</v>
+        <v>17.1131</v>
       </c>
       <c r="C19" t="n">
-        <v>-39.1722</v>
+        <v>-39.4854</v>
       </c>
       <c r="D19" t="n">
-        <v>74.2118</v>
+        <v>73.7116</v>
       </c>
       <c r="E19" t="n">
-        <v>28.8969</v>
+        <v>28.8485</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6063</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.544434</v>
+        <v>0.553153</v>
       </c>
     </row>
     <row r="20">
@@ -1243,22 +1243,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.209300000000001</v>
+        <v>13.9447</v>
       </c>
       <c r="C20" t="n">
-        <v>-31.541</v>
+        <v>-27.0064</v>
       </c>
       <c r="D20" t="n">
-        <v>49.9597</v>
+        <v>54.8959</v>
       </c>
       <c r="E20" t="n">
-        <v>20.7711</v>
+        <v>20.873</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4434</v>
+        <v>0.6681</v>
       </c>
       <c r="G20" t="n">
-        <v>0.657574</v>
+        <v>0.504212</v>
       </c>
     </row>
     <row r="21">
@@ -1268,22 +1268,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-20.3334</v>
+        <v>-20.3696</v>
       </c>
       <c r="C21" t="n">
-        <v>-77.0834</v>
+        <v>-77.03570000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>36.4165</v>
+        <v>36.2965</v>
       </c>
       <c r="E21" t="n">
-        <v>28.9264</v>
+        <v>28.8829</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7029</v>
+        <v>-0.7052</v>
       </c>
       <c r="G21" t="n">
-        <v>0.482227</v>
+        <v>0.480792</v>
       </c>
     </row>
     <row r="22">
@@ -1293,22 +1293,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20.1721</v>
+        <v>19.5279</v>
       </c>
       <c r="C22" t="n">
-        <v>-36.6348</v>
+        <v>-37.2459</v>
       </c>
       <c r="D22" t="n">
-        <v>76.979</v>
+        <v>76.3018</v>
       </c>
       <c r="E22" t="n">
-        <v>28.9554</v>
+        <v>28.9379</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6967</v>
+        <v>0.6748</v>
       </c>
       <c r="G22" t="n">
-        <v>0.486146</v>
+        <v>0.499917</v>
       </c>
     </row>
     <row r="23">
@@ -1318,22 +1318,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.749</v>
+        <v>34.6706</v>
       </c>
       <c r="C23" t="n">
-        <v>-24.0463</v>
+        <v>-22.0236</v>
       </c>
       <c r="D23" t="n">
-        <v>89.5442</v>
+        <v>91.3648</v>
       </c>
       <c r="E23" t="n">
-        <v>28.9495</v>
+        <v>28.8973</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1312</v>
+        <v>1.1998</v>
       </c>
       <c r="G23" t="n">
-        <v>0.25817</v>
+        <v>0.230455</v>
       </c>
     </row>
     <row r="24">
@@ -1343,22 +1343,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>67.223</v>
+        <v>68.2469</v>
       </c>
       <c r="C24" t="n">
-        <v>10.3333</v>
+        <v>11.3802</v>
       </c>
       <c r="D24" t="n">
-        <v>124.1126</v>
+        <v>125.1136</v>
       </c>
       <c r="E24" t="n">
-        <v>28.9976</v>
+        <v>28.9852</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3182</v>
+        <v>2.3545</v>
       </c>
       <c r="G24" t="n">
-        <v>0.020599</v>
+        <v>0.018704</v>
       </c>
     </row>
     <row r="25">
@@ -1368,22 +1368,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>15.0469</v>
+        <v>14.7059</v>
       </c>
       <c r="C25" t="n">
-        <v>-28.3288</v>
+        <v>-28.5932</v>
       </c>
       <c r="D25" t="n">
-        <v>58.4227</v>
+        <v>58.0051</v>
       </c>
       <c r="E25" t="n">
-        <v>22.1094</v>
+        <v>22.0697</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6806</v>
+        <v>0.6663</v>
       </c>
       <c r="G25" t="n">
-        <v>0.496271</v>
+        <v>0.505321</v>
       </c>
     </row>
     <row r="26">
@@ -1393,22 +1393,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-13.8553</v>
+        <v>-14.5181</v>
       </c>
       <c r="C26" t="n">
-        <v>-60.2159</v>
+        <v>-60.8016</v>
       </c>
       <c r="D26" t="n">
-        <v>32.5053</v>
+        <v>31.7655</v>
       </c>
       <c r="E26" t="n">
-        <v>23.6308</v>
+        <v>23.5909</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5863</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>0.557763</v>
+        <v>0.538399</v>
       </c>
     </row>
     <row r="27">
@@ -1418,22 +1418,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.6286</v>
+        <v>7.0426</v>
       </c>
       <c r="C27" t="n">
-        <v>-38.6932</v>
+        <v>-39.1961</v>
       </c>
       <c r="D27" t="n">
-        <v>53.9503</v>
+        <v>53.2813</v>
       </c>
       <c r="E27" t="n">
-        <v>23.611</v>
+        <v>23.5681</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3231</v>
+        <v>0.2988</v>
       </c>
       <c r="G27" t="n">
-        <v>0.746678</v>
+        <v>0.765128</v>
       </c>
     </row>
     <row r="28">
@@ -1443,22 +1443,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7.689</v>
+        <v>7.7202</v>
       </c>
       <c r="C28" t="n">
-        <v>-35.1827</v>
+        <v>-35.0746</v>
       </c>
       <c r="D28" t="n">
-        <v>50.5608</v>
+        <v>50.515</v>
       </c>
       <c r="E28" t="n">
-        <v>21.8525</v>
+        <v>21.8127</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3519</v>
+        <v>0.3539</v>
       </c>
       <c r="G28" t="n">
-        <v>0.725002</v>
+        <v>0.723453</v>
       </c>
     </row>
     <row r="29">
@@ -1468,672 +1468,647 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.798</v>
+        <v>-0.1185</v>
       </c>
       <c r="C29" t="n">
-        <v>-37.6623</v>
+        <v>-40.5521</v>
       </c>
       <c r="D29" t="n">
-        <v>43.2584</v>
+        <v>40.3151</v>
       </c>
       <c r="E29" t="n">
-        <v>20.6233</v>
+        <v>20.6092</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1357</v>
+        <v>-0.0057</v>
       </c>
       <c r="G29" t="n">
-        <v>0.892101</v>
+        <v>0.995413</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Model_LightSpeed16</t>
+          <t>Model_MX 16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7.0881</v>
+        <v>6.0456</v>
       </c>
       <c r="C30" t="n">
-        <v>-49.7655</v>
+        <v>-50.5767</v>
       </c>
       <c r="D30" t="n">
-        <v>63.9417</v>
+        <v>62.6678</v>
       </c>
       <c r="E30" t="n">
-        <v>28.9792</v>
+        <v>28.8606</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2446</v>
+        <v>0.2095</v>
       </c>
       <c r="G30" t="n">
-        <v>0.806812</v>
+        <v>0.834113</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Model_MX 16</t>
+          <t>Model_Optima CT660</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6.0363</v>
+        <v>14.0481</v>
       </c>
       <c r="C31" t="n">
-        <v>-50.6935</v>
+        <v>-29.7253</v>
       </c>
       <c r="D31" t="n">
-        <v>62.7661</v>
+        <v>57.8216</v>
       </c>
       <c r="E31" t="n">
-        <v>28.9161</v>
+        <v>22.3115</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2088</v>
+        <v>0.6296</v>
       </c>
       <c r="G31" t="n">
-        <v>0.834676</v>
+        <v>0.529051</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Model_Optima CT660</t>
+          <t>Model_Revolution CT</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>12.1257</v>
+        <v>4.8961</v>
       </c>
       <c r="C32" t="n">
-        <v>-31.1644</v>
+        <v>-36.1407</v>
       </c>
       <c r="D32" t="n">
-        <v>55.4159</v>
+        <v>45.933</v>
       </c>
       <c r="E32" t="n">
-        <v>22.0657</v>
+        <v>20.9166</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5495</v>
+        <v>0.2341</v>
       </c>
       <c r="G32" t="n">
-        <v>0.582742</v>
+        <v>0.814964</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Model_Revolution CT</t>
+          <t>Model_Revolution EVO</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5.39</v>
+        <v>-2.5822</v>
       </c>
       <c r="C33" t="n">
-        <v>-35.7108</v>
+        <v>-42.8809</v>
       </c>
       <c r="D33" t="n">
-        <v>46.4907</v>
+        <v>37.7165</v>
       </c>
       <c r="E33" t="n">
-        <v>20.9497</v>
+        <v>20.5404</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2573</v>
+        <v>-0.1257</v>
       </c>
       <c r="G33" t="n">
-        <v>0.797005</v>
+        <v>0.89998</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Model_Revolution EVO</t>
+          <t>Model_Revolution Frontier</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.9149</v>
+        <v>-27.5225</v>
       </c>
       <c r="C34" t="n">
-        <v>-42.2763</v>
+        <v>-84.1765</v>
       </c>
       <c r="D34" t="n">
-        <v>38.4465</v>
+        <v>29.1314</v>
       </c>
       <c r="E34" t="n">
-        <v>20.5729</v>
+        <v>28.8768</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0931</v>
+        <v>-0.9530999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>0.925857</v>
+        <v>0.340728</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Model_Revolution Frontier</t>
+          <t>Model_Revolution HD</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-27.6398</v>
+        <v>9.8079</v>
       </c>
       <c r="C35" t="n">
-        <v>-84.3844</v>
+        <v>-46.787</v>
       </c>
       <c r="D35" t="n">
-        <v>29.1048</v>
+        <v>66.4028</v>
       </c>
       <c r="E35" t="n">
-        <v>28.9237</v>
+        <v>28.8466</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9556</v>
+        <v>0.34</v>
       </c>
       <c r="G35" t="n">
-        <v>0.339455</v>
+        <v>0.733915</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Model_Revolution HD</t>
+          <t>Model_SOMATOM Definition</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9.3949</v>
+        <v>12.11</v>
       </c>
       <c r="C36" t="n">
-        <v>-47.307</v>
+        <v>-37.0349</v>
       </c>
       <c r="D36" t="n">
-        <v>66.0968</v>
+        <v>61.2548</v>
       </c>
       <c r="E36" t="n">
-        <v>28.9019</v>
+        <v>25.0493</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3251</v>
+        <v>0.4834</v>
       </c>
       <c r="G36" t="n">
-        <v>0.74519</v>
+        <v>0.628868</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition</t>
+          <t>Model_SOMATOM Definition AS</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>13.3491</v>
+        <v>17.7004</v>
       </c>
       <c r="C37" t="n">
-        <v>-35.8727</v>
+        <v>-31.4733</v>
       </c>
       <c r="D37" t="n">
-        <v>62.5709</v>
+        <v>66.8741</v>
       </c>
       <c r="E37" t="n">
-        <v>25.0892</v>
+        <v>25.064</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5321</v>
+        <v>0.7062</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5947750000000001</v>
+        <v>0.480196</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS</t>
+          <t>Model_SOMATOM Definition AS+</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16.866</v>
+        <v>9.9321</v>
       </c>
       <c r="C38" t="n">
-        <v>-32.3915</v>
+        <v>-30.2237</v>
       </c>
       <c r="D38" t="n">
-        <v>66.12350000000001</v>
+        <v>50.0878</v>
       </c>
       <c r="E38" t="n">
-        <v>25.1074</v>
+        <v>20.4676</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6718</v>
+        <v>0.4853</v>
       </c>
       <c r="G38" t="n">
-        <v>0.501865</v>
+        <v>0.62758</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS+</t>
+          <t>Model_SOMATOM Definition Edge</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10.283</v>
+        <v>17.7918</v>
       </c>
       <c r="C39" t="n">
-        <v>-29.9342</v>
+        <v>-26.1272</v>
       </c>
       <c r="D39" t="n">
-        <v>50.5001</v>
+        <v>61.7107</v>
       </c>
       <c r="E39" t="n">
-        <v>20.4994</v>
+        <v>22.3856</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5016</v>
+        <v>0.7948</v>
       </c>
       <c r="G39" t="n">
-        <v>0.61602</v>
+        <v>0.426895</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Edge</t>
+          <t>Model_SOMATOM Definition Flash</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>18.3193</v>
+        <v>13.404</v>
       </c>
       <c r="C40" t="n">
-        <v>-25.6717</v>
+        <v>-26.7026</v>
       </c>
       <c r="D40" t="n">
-        <v>62.3102</v>
+        <v>53.5107</v>
       </c>
       <c r="E40" t="n">
-        <v>22.4229</v>
+        <v>20.4425</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>0.414091</v>
+        <v>0.512146</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Flash</t>
+          <t>Model_SOMATOM Drive</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>13.4756</v>
+        <v>26.4174</v>
       </c>
       <c r="C41" t="n">
-        <v>-26.6968</v>
+        <v>-30.1334</v>
       </c>
       <c r="D41" t="n">
-        <v>53.6481</v>
+        <v>82.9682</v>
       </c>
       <c r="E41" t="n">
-        <v>20.4766</v>
+        <v>28.8242</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6581</v>
+        <v>0.9165</v>
       </c>
       <c r="G41" t="n">
-        <v>0.510595</v>
+        <v>0.359586</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Drive</t>
+          <t>Model_SOMATOM Emotion 16</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.2153</v>
+        <v>34.3823</v>
       </c>
       <c r="C42" t="n">
-        <v>-30.4434</v>
+        <v>-22.2421</v>
       </c>
       <c r="D42" t="n">
-        <v>82.874</v>
+        <v>91.0067</v>
       </c>
       <c r="E42" t="n">
-        <v>28.8799</v>
+        <v>28.8617</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9077</v>
+        <v>1.1913</v>
       </c>
       <c r="G42" t="n">
-        <v>0.364194</v>
+        <v>0.233777</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Emotion 16</t>
+          <t>Model_SOMATOM Force</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>33.8313</v>
+        <v>18.5364</v>
       </c>
       <c r="C43" t="n">
-        <v>-22.8994</v>
+        <v>-21.6069</v>
       </c>
       <c r="D43" t="n">
-        <v>90.562</v>
+        <v>58.6797</v>
       </c>
       <c r="E43" t="n">
-        <v>28.9166</v>
+        <v>20.4612</v>
       </c>
       <c r="F43" t="n">
-        <v>1.17</v>
+        <v>0.9059</v>
       </c>
       <c r="G43" t="n">
-        <v>0.24224</v>
+        <v>0.365153</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Force</t>
+          <t>Model_SOMATOM Perspective</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18.2883</v>
+        <v>10.4689</v>
       </c>
       <c r="C44" t="n">
-        <v>-21.9261</v>
+        <v>-32.3001</v>
       </c>
       <c r="D44" t="n">
-        <v>58.5026</v>
+        <v>53.2379</v>
       </c>
       <c r="E44" t="n">
-        <v>20.4979</v>
+        <v>21.7995</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8922</v>
+        <v>0.4802</v>
       </c>
       <c r="G44" t="n">
-        <v>0.372458</v>
+        <v>0.631148</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Perspective</t>
+          <t>Model_SOMATOM Scope</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10.2163</v>
+        <v>16.1939</v>
       </c>
       <c r="C45" t="n">
-        <v>-32.6306</v>
+        <v>-30.0131</v>
       </c>
       <c r="D45" t="n">
-        <v>53.0632</v>
+        <v>62.4008</v>
       </c>
       <c r="E45" t="n">
-        <v>21.8398</v>
+        <v>23.5519</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4678</v>
+        <v>0.6876</v>
       </c>
       <c r="G45" t="n">
-        <v>0.640021</v>
+        <v>0.491846</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Scope</t>
+          <t>Model_SOMATOM go.Top</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>15.672</v>
+        <v>-4.1877</v>
       </c>
       <c r="C46" t="n">
-        <v>-30.622</v>
+        <v>-61.1032</v>
       </c>
       <c r="D46" t="n">
-        <v>61.966</v>
+        <v>52.7277</v>
       </c>
       <c r="E46" t="n">
-        <v>23.5968</v>
+        <v>29.01</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6642</v>
+        <v>-0.1444</v>
       </c>
       <c r="G46" t="n">
-        <v>0.506713</v>
+        <v>0.885244</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Model_SOMATOM go.Top</t>
+          <t>Model_Scope</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-5.1436</v>
+        <v>25.0103</v>
       </c>
       <c r="C47" t="n">
-        <v>-62.0923</v>
+        <v>-31.5753</v>
       </c>
       <c r="D47" t="n">
-        <v>51.8051</v>
+        <v>81.5959</v>
       </c>
       <c r="E47" t="n">
-        <v>29.0277</v>
+        <v>28.8419</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.1772</v>
+        <v>0.8672</v>
       </c>
       <c r="G47" t="n">
-        <v>0.859382</v>
+        <v>0.386031</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Model_Scope</t>
+          <t>Model_Sensation 16</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>24.0459</v>
+        <v>42.1122</v>
       </c>
       <c r="C48" t="n">
-        <v>-32.6459</v>
+        <v>-14.4521</v>
       </c>
       <c r="D48" t="n">
-        <v>80.7376</v>
+        <v>98.6765</v>
       </c>
       <c r="E48" t="n">
-        <v>28.8967</v>
+        <v>28.831</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8321</v>
+        <v>1.4607</v>
       </c>
       <c r="G48" t="n">
-        <v>0.405495</v>
+        <v>0.144369</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Model_Sensation 16</t>
+          <t>Model_Sensation 64</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>42.1782</v>
+        <v>5.3938</v>
       </c>
       <c r="C49" t="n">
-        <v>-14.4934</v>
+        <v>-34.9556</v>
       </c>
       <c r="D49" t="n">
-        <v>98.8497</v>
+        <v>45.7431</v>
       </c>
       <c r="E49" t="n">
-        <v>28.8864</v>
+        <v>20.5662</v>
       </c>
       <c r="F49" t="n">
-        <v>1.4601</v>
+        <v>0.2623</v>
       </c>
       <c r="G49" t="n">
-        <v>0.144505</v>
+        <v>0.793163</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Model_Sensation 64</t>
+          <t>Model_Sensation Open</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5.7396</v>
+        <v>27.0033</v>
       </c>
       <c r="C50" t="n">
-        <v>-34.6799</v>
+        <v>-16.9372</v>
       </c>
       <c r="D50" t="n">
-        <v>46.1591</v>
+        <v>70.94370000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>20.6025</v>
+        <v>22.3966</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2786</v>
+        <v>1.2057</v>
       </c>
       <c r="G50" t="n">
-        <v>0.7806070000000001</v>
+        <v>0.228175</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Model_Sensation Open</t>
+          <t>Model_Spirit</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26.3187</v>
+        <v>-0.2857</v>
       </c>
       <c r="C51" t="n">
-        <v>-17.6755</v>
+        <v>-56.9127</v>
       </c>
       <c r="D51" t="n">
-        <v>70.3128</v>
+        <v>56.3412</v>
       </c>
       <c r="E51" t="n">
-        <v>22.4245</v>
+        <v>28.863</v>
       </c>
       <c r="F51" t="n">
-        <v>1.1737</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>0.240758</v>
+        <v>0.992104</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Model_Spirit</t>
+          <t>Model_Supria</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.0344</v>
+        <v>3.6443</v>
       </c>
       <c r="C52" t="n">
-        <v>-57.7668</v>
+        <v>-53.1504</v>
       </c>
       <c r="D52" t="n">
-        <v>55.698</v>
+        <v>60.4389</v>
       </c>
       <c r="E52" t="n">
-        <v>28.9175</v>
+        <v>28.9485</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.0358</v>
+        <v>0.1259</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9714699999999999</v>
+        <v>0.899841</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Model_Supria</t>
+          <t>Model_iCT 256</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6846</v>
+        <v>10.2599</v>
       </c>
       <c r="C53" t="n">
-        <v>-56.1953</v>
+        <v>-29.8333</v>
       </c>
       <c r="D53" t="n">
-        <v>57.5645</v>
+        <v>50.353</v>
       </c>
       <c r="E53" t="n">
-        <v>28.9926</v>
+        <v>20.4357</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0236</v>
+        <v>0.5021</v>
       </c>
       <c r="G53" t="n">
-        <v>0.981166</v>
+        <v>0.615719</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Model_iCT 256</t>
+          <t>Model_iCT SP</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10.6156</v>
+        <v>-30.0625</v>
       </c>
       <c r="C54" t="n">
-        <v>-29.5439</v>
+        <v>-86.7127</v>
       </c>
       <c r="D54" t="n">
-        <v>50.7751</v>
+        <v>26.5877</v>
       </c>
       <c r="E54" t="n">
-        <v>20.47</v>
+        <v>28.8748</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5185999999999999</v>
+        <v>-1.0411</v>
       </c>
       <c r="G54" t="n">
-        <v>0.604137</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Model_iCT SP</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>-29.3183</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-86.0736</v>
-      </c>
-      <c r="D55" t="n">
-        <v>27.437</v>
-      </c>
-      <c r="E55" t="n">
-        <v>28.9291</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-1.0135</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.311041</v>
+        <v>0.298023</v>
       </c>
     </row>
   </sheetData>
@@ -2174,7 +2149,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1297</v>
+        <v>1265</v>
       </c>
       <c r="C2" t="inlineStr"/>
     </row>
@@ -2185,7 +2160,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5814</v>
+        <v>0.584</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2200,7 +2175,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5636</v>
+        <v>0.5661</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2215,7 +2190,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.5792</v>
+        <v>32.7138</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2245,7 +2220,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11558.01</v>
+        <v>11268.24</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2260,7 +2235,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11837.08</v>
+        <v>11540.81</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2275,7 +2250,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.9873</v>
+        <v>19.9457</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2290,7 +2265,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14.6877</v>
+        <v>14.6597</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2305,7 +2280,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5305</v>
+        <v>0.5423</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2320,7 +2295,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0483</v>
+        <v>0.0541</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2346,7 +2321,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2361,7 +2336,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9384</v>
+        <v>0.9598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2404,7 +2379,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>100.5504</v>
+        <v>98.1503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2419,7 +2394,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.8e-05</v>
+        <v>0.000115</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2447,7 +2422,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0268</v>
+        <v>2.0341</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2475,7 +2450,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>379.4</v>
+        <v>366.96</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
